--- a/02_DIA_inicio_2026_analisis_assets/rbd_9419_liceo-municipal-enrique-backausse_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9419_liceo-municipal-enrique-backausse_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7074FED1-51E3-4846-AA2D-C24C4A6323A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E2CBBB7-DC14-42A8-83FE-FAA46CE64703}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD0D43E9-D0E4-4EF1-A0EB-BA6CF612EED1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE2585B1-6E74-4F38-86BF-8170906EE4CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA02805A-C33F-4532-B9E4-6BC9F492EF62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60D53CBA-D1CF-47CD-8F96-994C652EE701}"/>
 </file>